--- a/salidas/empresas/COST.xlsx
+++ b/salidas/empresas/COST.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>33.75137329101562</v>
+        <v>33.7513542175293</v>
       </c>
       <c r="C2" t="n">
         <v>49.88999938964844</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>34.71186447143555</v>
+        <v>34.71184158325195</v>
       </c>
       <c r="C3" t="n">
         <v>51.18999862670898</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>36.72579574584961</v>
+        <v>36.72581100463867</v>
       </c>
       <c r="C4" t="n">
         <v>54.15999984741211</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>36.90890121459961</v>
+        <v>36.90888977050781</v>
       </c>
       <c r="C5" t="n">
         <v>54.43000030517578</v>
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>38.82877349853516</v>
+        <v>38.82878112792969</v>
       </c>
       <c r="C7" t="n">
         <v>57.13000106811523</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>35.94952011108398</v>
+        <v>35.94950485229492</v>
       </c>
       <c r="C8" t="n">
         <v>52.7599983215332</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>31.88169097900391</v>
+        <v>31.88167762756348</v>
       </c>
       <c r="C9" t="n">
         <v>46.79000091552734</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>33.85086822509766</v>
+        <v>33.85087585449219</v>
       </c>
       <c r="C10" t="n">
         <v>49.68000030517578</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>36.37197113037109</v>
+        <v>36.37196731567383</v>
       </c>
       <c r="C11" t="n">
         <v>53.38000106811523</v>
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>36.11401748657227</v>
+        <v>36.11402130126953</v>
       </c>
       <c r="C13" t="n">
         <v>52.86999893188477</v>
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>36.86217498779297</v>
+        <v>36.8621940612793</v>
       </c>
       <c r="C16" t="n">
         <v>53.84000015258789</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>36.77561950683594</v>
+        <v>36.77563095092773</v>
       </c>
       <c r="C17" t="n">
         <v>53.56999969482422</v>
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>40.17378234863281</v>
+        <v>40.17378616333008</v>
       </c>
       <c r="C19" t="n">
         <v>58.52000045776367</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>41.15171432495117</v>
+        <v>41.15170669555664</v>
       </c>
       <c r="C20" t="n">
         <v>59.79999923706055</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>42.49359893798828</v>
+        <v>42.49361038208008</v>
       </c>
       <c r="C21" t="n">
         <v>61.75</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>42.23209762573242</v>
+        <v>42.23208999633789</v>
       </c>
       <c r="C22" t="n">
         <v>61.36999893188477</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>46.28533172607422</v>
+        <v>46.28533554077148</v>
       </c>
       <c r="C23" t="n">
         <v>67.26000213623047</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>46.48389053344727</v>
+        <v>46.48387908935547</v>
       </c>
       <c r="C24" t="n">
         <v>67.40000152587891</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>48.11152648925781</v>
+        <v>48.11151123046875</v>
       </c>
       <c r="C25" t="n">
         <v>69.76000213623047</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>46.85630035400391</v>
+        <v>46.85631561279297</v>
       </c>
       <c r="C26" t="n">
         <v>67.94000244140625</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>42.80083084106445</v>
+        <v>42.80083847045898</v>
       </c>
       <c r="C27" t="n">
         <v>61.91999816894531</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>44.90908050537109</v>
+        <v>44.90909194946289</v>
       </c>
       <c r="C28" t="n">
         <v>64.97000122070312</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>49.2500114440918</v>
+        <v>49.25</v>
       </c>
       <c r="C29" t="n">
         <v>71.25</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>49.40523147583008</v>
+        <v>49.40524673461914</v>
       </c>
       <c r="C30" t="n">
         <v>71.31999969482422</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>48.58781051635742</v>
+        <v>48.58781814575195</v>
       </c>
       <c r="C31" t="n">
         <v>70.13999938964844</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>43.42008209228516</v>
+        <v>43.42007827758789</v>
       </c>
       <c r="C32" t="n">
         <v>62.68000030517578</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>46.56950759887695</v>
+        <v>46.56951522827148</v>
       </c>
       <c r="C33" t="n">
         <v>67.05999755859375</v>
@@ -1090,7 +1102,7 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>39.5903434753418</v>
+        <v>39.59035110473633</v>
       </c>
       <c r="C35" t="n">
         <v>57.0099983215332</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>35.85283660888672</v>
+        <v>35.85284042358398</v>
       </c>
       <c r="C36" t="n">
         <v>51.47000122070312</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>36.5703010559082</v>
+        <v>36.57030487060547</v>
       </c>
       <c r="C37" t="n">
         <v>52.5</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>31.36686515808105</v>
+        <v>31.36686706542969</v>
       </c>
       <c r="C38" t="n">
         <v>45.02999877929688</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>29.60079002380371</v>
+        <v>29.60079765319824</v>
       </c>
       <c r="C39" t="n">
         <v>42.34000015258789</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>32.38328552246094</v>
+        <v>32.38330459594727</v>
       </c>
       <c r="C40" t="n">
         <v>46.31999969482422</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>33.97730255126953</v>
+        <v>33.9772834777832</v>
       </c>
       <c r="C41" t="n">
         <v>48.59999847412109</v>
@@ -1242,7 +1254,7 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>32.12906265258789</v>
+        <v>32.12904739379883</v>
       </c>
       <c r="C43" t="n">
         <v>45.77999877929688</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>34.73980712890625</v>
+        <v>34.73979187011719</v>
       </c>
       <c r="C44" t="n">
         <v>49.5</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>35.91061401367188</v>
+        <v>35.91061019897461</v>
       </c>
       <c r="C45" t="n">
         <v>50.97999954223633</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>39.71442794799805</v>
+        <v>39.71441650390625</v>
       </c>
       <c r="C46" t="n">
         <v>56.38000106811523</v>
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>40.16784286499023</v>
+        <v>40.1678352355957</v>
       </c>
       <c r="C47" t="n">
         <v>56.84999847412109</v>
@@ -1356,7 +1368,7 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1375,11 +1387,11 @@
       <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>41.80704498291016</v>
+        <v>41.80706405639648</v>
       </c>
       <c r="C49" t="n">
         <v>59.16999816894531</v>
@@ -1400,11 +1412,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>40.57764053344727</v>
+        <v>40.57765579223633</v>
       </c>
       <c r="C50" t="n">
         <v>57.43000030517578</v>
@@ -1425,11 +1437,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>43.21123886108398</v>
+        <v>43.21122741699219</v>
       </c>
       <c r="C51" t="n">
         <v>60.97000122070312</v>
@@ -1450,11 +1462,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>42.3182373046875</v>
+        <v>42.31822204589844</v>
       </c>
       <c r="C52" t="n">
         <v>59.70999908447266</v>
@@ -1475,11 +1487,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>41.87173461914062</v>
+        <v>41.87173080444336</v>
       </c>
       <c r="C53" t="n">
         <v>59.08000183105469</v>
@@ -1500,11 +1512,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>41.42531585693359</v>
+        <v>41.42530822753906</v>
       </c>
       <c r="C54" t="n">
         <v>58.25</v>
@@ -1525,11 +1537,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>38.99313354492188</v>
+        <v>38.99311447143555</v>
       </c>
       <c r="C55" t="n">
         <v>54.83000183105469</v>
@@ -1550,11 +1562,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>40.33012008666992</v>
+        <v>40.33012390136719</v>
       </c>
       <c r="C56" t="n">
         <v>56.70999908447266</v>
@@ -1575,11 +1587,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>40.32694625854492</v>
+        <v>40.32695007324219</v>
       </c>
       <c r="C57" t="n">
         <v>56.5</v>
@@ -1600,7 +1612,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1625,11 +1637,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>44.94688415527344</v>
+        <v>44.94686889648438</v>
       </c>
       <c r="C59" t="n">
         <v>62.77000045776367</v>
@@ -1654,11 +1666,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>48.4125862121582</v>
+        <v>48.41259384155273</v>
       </c>
       <c r="C60" t="n">
         <v>67.61000061035156</v>
@@ -1683,11 +1695,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>51.70644760131836</v>
+        <v>51.70645523071289</v>
       </c>
       <c r="C61" t="n">
         <v>72.20999908447266</v>
@@ -1712,11 +1724,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>51.4415283203125</v>
+        <v>51.44150924682617</v>
       </c>
       <c r="C62" t="n">
         <v>71.83999633789062</v>
@@ -1741,11 +1753,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>53.70105361938477</v>
+        <v>53.70106506347656</v>
       </c>
       <c r="C63" t="n">
         <v>74.79000091552734</v>
@@ -1770,11 +1782,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>52.64557647705078</v>
+        <v>52.64556884765625</v>
       </c>
       <c r="C64" t="n">
         <v>73.31999969482422</v>
@@ -1799,11 +1811,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>58.08099365234375</v>
+        <v>58.08102035522461</v>
       </c>
       <c r="C65" t="n">
         <v>80.88999938964844</v>
@@ -1828,11 +1840,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>59.39601898193359</v>
+        <v>59.39602279663086</v>
       </c>
       <c r="C66" t="n">
         <v>82.48000335693359</v>
@@ -1857,11 +1869,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>58.5030632019043</v>
+        <v>58.5030517578125</v>
       </c>
       <c r="C67" t="n">
         <v>81.23999786376953</v>
@@ -1886,11 +1898,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>56.34989547729492</v>
+        <v>56.34987640380859</v>
       </c>
       <c r="C68" t="n">
         <v>78.25</v>
@@ -1915,11 +1927,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>56.73828506469727</v>
+        <v>56.73828887939453</v>
       </c>
       <c r="C69" t="n">
         <v>78.54000091552734</v>
@@ -1944,7 +1956,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1973,11 +1985,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>60.14086151123047</v>
+        <v>60.14086532592773</v>
       </c>
       <c r="C71" t="n">
         <v>83.25</v>
@@ -2002,11 +2014,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>61.79803848266602</v>
+        <v>61.79804611206055</v>
       </c>
       <c r="C72" t="n">
         <v>85.30000305175781</v>
@@ -2031,11 +2043,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>60.36356353759766</v>
+        <v>60.36356735229492</v>
       </c>
       <c r="C73" t="n">
         <v>83.31999969482422</v>
@@ -2060,11 +2072,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>59.60282897949219</v>
+        <v>59.60287094116211</v>
       </c>
       <c r="C74" t="n">
         <v>82.26999664306641</v>
@@ -2089,7 +2101,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2118,11 +2130,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>65.96990966796875</v>
+        <v>65.96990203857422</v>
       </c>
       <c r="C76" t="n">
         <v>90.80000305175781</v>
@@ -2147,11 +2159,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>64.06638336181641</v>
+        <v>64.06636047363281</v>
       </c>
       <c r="C77" t="n">
         <v>88.18000030517578</v>
@@ -2176,11 +2188,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>62.97353363037109</v>
+        <v>62.97356796264648</v>
       </c>
       <c r="C78" t="n">
         <v>86.38999938964844</v>
@@ -2205,11 +2217,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>69.24979400634766</v>
+        <v>69.249755859375</v>
       </c>
       <c r="C79" t="n">
         <v>95</v>
@@ -2234,11 +2246,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>70.10992431640625</v>
+        <v>70.10994720458984</v>
       </c>
       <c r="C80" t="n">
         <v>96.18000030517578</v>
@@ -2263,11 +2275,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>71.5472412109375</v>
+        <v>71.54723358154297</v>
       </c>
       <c r="C81" t="n">
         <v>97.87000274658203</v>
@@ -2292,11 +2304,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>73.22132873535156</v>
+        <v>73.22129821777344</v>
       </c>
       <c r="C82" t="n">
         <v>100.1600036621094</v>
@@ -2321,11 +2333,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>71.95661926269531</v>
+        <v>71.95658874511719</v>
       </c>
       <c r="C83" t="n">
         <v>98.43000030517578</v>
@@ -2350,11 +2362,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>76.18900299072266</v>
+        <v>76.18898010253906</v>
       </c>
       <c r="C84" t="n">
         <v>103.9199981689453</v>
@@ -2379,11 +2391,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>77.50457763671875</v>
+        <v>77.50460815429688</v>
       </c>
       <c r="C85" t="n">
         <v>98.73000335693359</v>
@@ -2408,11 +2420,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>80.33853149414062</v>
+        <v>80.33848571777344</v>
       </c>
       <c r="C86" t="n">
         <v>102.3399963378906</v>
@@ -2437,11 +2449,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>79.72644805908203</v>
+        <v>79.7264404296875</v>
       </c>
       <c r="C87" t="n">
         <v>101.2900009155273</v>
@@ -2466,11 +2478,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>83.52030944824219</v>
+        <v>83.52032470703125</v>
       </c>
       <c r="C88" t="n">
         <v>106.1100006103516</v>
@@ -2495,7 +2507,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2524,11 +2536,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>86.53176879882812</v>
+        <v>86.53177642822266</v>
       </c>
       <c r="C90" t="n">
         <v>109.629997253418</v>
@@ -2553,11 +2565,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>87.27371215820312</v>
+        <v>87.27370452880859</v>
       </c>
       <c r="C91" t="n">
         <v>110.5699996948242</v>
@@ -2582,7 +2594,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2611,11 +2623,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>88.52945709228516</v>
+        <v>88.52947998046875</v>
       </c>
       <c r="C93" t="n">
         <v>111.870002746582</v>
@@ -2640,11 +2652,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>91.14095306396484</v>
+        <v>91.14096069335938</v>
       </c>
       <c r="C94" t="n">
         <v>115.1699981689453</v>
@@ -2669,7 +2681,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2698,7 +2710,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2727,11 +2739,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>94.42675018310547</v>
+        <v>94.4267578125</v>
       </c>
       <c r="C97" t="n">
         <v>119.0199966430664</v>
@@ -2756,11 +2768,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>89.14289855957031</v>
+        <v>89.14291381835938</v>
       </c>
       <c r="C98" t="n">
         <v>112.3600006103516</v>
@@ -2785,11 +2797,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>92.91597747802734</v>
+        <v>92.91596984863281</v>
       </c>
       <c r="C99" t="n">
         <v>116.8000030517578</v>
@@ -2814,11 +2826,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>88.84292602539062</v>
+        <v>88.84293365478516</v>
       </c>
       <c r="C100" t="n">
         <v>111.6800003051758</v>
@@ -2843,11 +2855,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>92.02498626708984</v>
+        <v>92.02500152587891</v>
       </c>
       <c r="C101" t="n">
         <v>115.6800003051758</v>
@@ -2872,11 +2884,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>92.57807159423828</v>
+        <v>92.57810974121094</v>
       </c>
       <c r="C102" t="n">
         <v>116.0199966430664</v>
@@ -2901,11 +2913,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>91.89185333251953</v>
+        <v>91.89183807373047</v>
       </c>
       <c r="C103" t="n">
         <v>115.1600036621094</v>
@@ -2930,11 +2942,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>94.07527923583984</v>
+        <v>94.07529449462891</v>
       </c>
       <c r="C104" t="n">
         <v>117.5400009155273</v>
@@ -2959,11 +2971,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>96.90859222412109</v>
+        <v>96.90858459472656</v>
       </c>
       <c r="C105" t="n">
         <v>121.0800018310547</v>
@@ -2988,7 +3000,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -3017,11 +3029,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>106.7450866699219</v>
+        <v>106.7450942993164</v>
       </c>
       <c r="C107" t="n">
         <v>133.3699951171875</v>
@@ -3046,11 +3058,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>114.0437088012695</v>
+        <v>114.0437545776367</v>
       </c>
       <c r="C108" t="n">
         <v>142.1199951171875</v>
@@ -3075,7 +3087,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3104,11 +3116,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>114.7419052124023</v>
+        <v>114.7418670654297</v>
       </c>
       <c r="C110" t="n">
         <v>142.9900054931641</v>
@@ -3133,11 +3145,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>122.1270599365234</v>
+        <v>122.1270523071289</v>
       </c>
       <c r="C111" t="n">
         <v>146.9600067138672</v>
@@ -3162,11 +3174,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>125.8998947143555</v>
+        <v>125.8999176025391</v>
       </c>
       <c r="C112" t="n">
         <v>151.5</v>
@@ -3191,11 +3203,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>119.203010559082</v>
+        <v>119.2029495239258</v>
       </c>
       <c r="C113" t="n">
         <v>143.0500030517578</v>
@@ -3220,11 +3232,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>118.8196487426758</v>
+        <v>118.8196334838867</v>
       </c>
       <c r="C114" t="n">
         <v>142.5899963378906</v>
@@ -3249,11 +3261,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>112.5449676513672</v>
+        <v>112.5449752807617</v>
       </c>
       <c r="C115" t="n">
         <v>135.0599975585938</v>
@@ -3278,11 +3290,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>121.0778732299805</v>
+        <v>121.0778961181641</v>
       </c>
       <c r="C116" t="n">
         <v>145.3000030517578</v>
@@ -3307,11 +3319,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>117.0239639282227</v>
+        <v>117.0239410400391</v>
       </c>
       <c r="C117" t="n">
         <v>140.0500030517578</v>
@@ -3336,11 +3348,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>120.8008193969727</v>
+        <v>120.8008117675781</v>
       </c>
       <c r="C118" t="n">
         <v>144.5700073242188</v>
@@ -3365,11 +3377,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>132.1230010986328</v>
+        <v>132.1230163574219</v>
       </c>
       <c r="C119" t="n">
         <v>158.1199951171875</v>
@@ -3394,7 +3406,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3423,11 +3435,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>135.2960815429688</v>
+        <v>135.2960357666016</v>
       </c>
       <c r="C121" t="n">
         <v>161.5</v>
@@ -3452,11 +3464,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>126.6002197265625</v>
+        <v>126.6002349853516</v>
       </c>
       <c r="C122" t="n">
         <v>151.1199951171875</v>
@@ -3481,11 +3493,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>126.0278778076172</v>
+        <v>126.0278701782227</v>
       </c>
       <c r="C123" t="n">
         <v>150.0299987792969</v>
@@ -3510,11 +3522,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>132.3699645996094</v>
+        <v>132.3700561523438</v>
       </c>
       <c r="C124" t="n">
         <v>157.5800018310547</v>
@@ -3539,11 +3551,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>124.7998657226562</v>
+        <v>124.7998886108398</v>
       </c>
       <c r="C125" t="n">
         <v>148.1300048828125</v>
@@ -3568,11 +3580,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>125.3390655517578</v>
+        <v>125.3390579223633</v>
       </c>
       <c r="C126" t="n">
         <v>148.7700042724609</v>
@@ -3597,11 +3609,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>132.3065032958984</v>
+        <v>132.3065643310547</v>
       </c>
       <c r="C127" t="n">
         <v>157.0399932861328</v>
@@ -3626,7 +3638,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3655,7 +3667,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3684,11 +3696,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>128.8353881835938</v>
+        <v>128.8354187011719</v>
       </c>
       <c r="C130" t="n">
         <v>152.5099945068359</v>
@@ -3713,11 +3725,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>124.9156494140625</v>
+        <v>124.9156723022461</v>
       </c>
       <c r="C131" t="n">
         <v>147.8699951171875</v>
@@ -3742,7 +3754,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3771,11 +3783,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>135.6719512939453</v>
+        <v>135.671875</v>
       </c>
       <c r="C133" t="n">
         <v>160.1100006103516</v>
@@ -3800,11 +3812,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>138.9258117675781</v>
+        <v>138.9258270263672</v>
       </c>
       <c r="C134" t="n">
         <v>163.9499969482422</v>
@@ -3829,7 +3841,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
@@ -3858,11 +3870,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>142.4777069091797</v>
+        <v>142.4776611328125</v>
       </c>
       <c r="C136" t="n">
         <v>167.6900024414062</v>
@@ -3887,11 +3899,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>150.8297424316406</v>
+        <v>150.8297729492188</v>
       </c>
       <c r="C137" t="n">
         <v>177.5200042724609</v>
@@ -3916,11 +3928,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>159.9612579345703</v>
+        <v>159.9612731933594</v>
       </c>
       <c r="C138" t="n">
         <v>180.4299926757812</v>
@@ -3945,7 +3957,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3974,11 +3986,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>140.5278625488281</v>
+        <v>140.5279388427734</v>
       </c>
       <c r="C140" t="n">
         <v>158.5099945068359</v>
@@ -4003,11 +4015,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>139.4029998779297</v>
+        <v>139.4029846191406</v>
       </c>
       <c r="C141" t="n">
         <v>156.7400054931641</v>
@@ -4032,11 +4044,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>146.1178588867188</v>
+        <v>146.1179046630859</v>
       </c>
       <c r="C142" t="n">
         <v>164.2899932861328</v>
@@ -4061,11 +4073,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>143.2629852294922</v>
+        <v>143.2629699707031</v>
       </c>
       <c r="C143" t="n">
         <v>161.0800018310547</v>
@@ -4090,7 +4102,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -4119,11 +4131,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>166.0245056152344</v>
+        <v>166.0244903564453</v>
       </c>
       <c r="C145" t="n">
         <v>186.1199951171875</v>
@@ -4148,11 +4160,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>173.8297424316406</v>
+        <v>173.8296966552734</v>
       </c>
       <c r="C146" t="n">
         <v>194.8699951171875</v>
@@ -4177,11 +4189,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>170.7439880371094</v>
+        <v>170.7440338134766</v>
       </c>
       <c r="C147" t="n">
         <v>190.8999938964844</v>
@@ -4206,11 +4218,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>168.5348815917969</v>
+        <v>168.5348510742188</v>
       </c>
       <c r="C148" t="n">
         <v>188.4299926757812</v>
@@ -4235,11 +4247,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>176.3430480957031</v>
+        <v>176.3430938720703</v>
       </c>
       <c r="C149" t="n">
         <v>197.1600036621094</v>
@@ -4264,7 +4276,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4293,11 +4305,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>187.4601440429688</v>
+        <v>187.4601287841797</v>
       </c>
       <c r="C151" t="n">
         <v>208.9799957275391</v>
@@ -4322,11 +4334,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>196.1882019042969</v>
+        <v>196.1881713867188</v>
       </c>
       <c r="C152" t="n">
         <v>218.7100067138672</v>
@@ -4351,11 +4363,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>209.6424255371094</v>
+        <v>209.6424102783203</v>
       </c>
       <c r="C153" t="n">
         <v>233.1300048828125</v>
@@ -4380,11 +4392,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>211.2161254882812</v>
+        <v>211.2161560058594</v>
       </c>
       <c r="C154" t="n">
         <v>234.8800048828125</v>
@@ -4409,11 +4421,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>205.5958099365234</v>
+        <v>205.5957946777344</v>
       </c>
       <c r="C155" t="n">
         <v>228.6300048828125</v>
@@ -4438,11 +4450,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>208.4731597900391</v>
+        <v>208.4731750488281</v>
       </c>
       <c r="C156" t="n">
         <v>231.2799987792969</v>
@@ -4467,11 +4479,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>183.6218719482422</v>
+        <v>183.6219024658203</v>
       </c>
       <c r="C157" t="n">
         <v>203.7100067138672</v>
@@ -4496,7 +4508,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -4525,7 +4537,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4554,11 +4566,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>218.8518218994141</v>
+        <v>218.8517761230469</v>
       </c>
       <c r="C160" t="n">
         <v>242.1399993896484</v>
@@ -4583,11 +4595,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>221.9157409667969</v>
+        <v>221.9157562255859</v>
       </c>
       <c r="C161" t="n">
         <v>245.5299987792969</v>
@@ -4612,11 +4624,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>217.1227874755859</v>
+        <v>217.1228179931641</v>
       </c>
       <c r="C162" t="n">
         <v>239.5800018310547</v>
@@ -4641,11 +4653,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>239.4894256591797</v>
+        <v>239.4894104003906</v>
       </c>
       <c r="C163" t="n">
         <v>264.260009765625</v>
@@ -4670,11 +4682,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>249.7936553955078</v>
+        <v>249.7935943603516</v>
       </c>
       <c r="C164" t="n">
         <v>275.6300048828125</v>
@@ -4699,11 +4711,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>267.7213745117188</v>
+        <v>267.7213134765625</v>
       </c>
       <c r="C165" t="n">
         <v>294.760009765625</v>
@@ -4728,11 +4740,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>261.6812744140625</v>
+        <v>261.681396484375</v>
       </c>
       <c r="C166" t="n">
         <v>288.1099853515625</v>
@@ -4757,11 +4769,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>270.4420166015625</v>
+        <v>270.4420776367188</v>
       </c>
       <c r="C167" t="n">
         <v>297.1099853515625</v>
@@ -4786,11 +4798,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>272.8996887207031</v>
+        <v>272.899658203125</v>
       </c>
       <c r="C168" t="n">
         <v>299.8099975585938</v>
@@ -4815,11 +4827,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>267.5384216308594</v>
+        <v>267.5383911132812</v>
       </c>
       <c r="C169" t="n">
         <v>293.9200134277344</v>
@@ -4844,11 +4856,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>278.0971374511719</v>
+        <v>278.0972290039062</v>
       </c>
       <c r="C170" t="n">
         <v>305.5199890136719</v>
@@ -4873,11 +4885,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>256.4450378417969</v>
+        <v>256.4450073242188</v>
       </c>
       <c r="C171" t="n">
         <v>281.1400146484375</v>
@@ -4902,11 +4914,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>260.0845642089844</v>
+        <v>260.0845031738281</v>
       </c>
       <c r="C172" t="n">
         <v>285.1300048828125</v>
@@ -4931,11 +4943,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>277.016357421875</v>
+        <v>277.0163879394531</v>
       </c>
       <c r="C173" t="n">
         <v>303</v>
@@ -4960,11 +4972,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>282.0172119140625</v>
+        <v>282.0171813964844</v>
       </c>
       <c r="C174" t="n">
         <v>308.4700012207031</v>
@@ -4989,11 +5001,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>277.2083129882812</v>
+        <v>277.2082824707031</v>
       </c>
       <c r="C175" t="n">
         <v>303.2099914550781</v>
@@ -5018,11 +5030,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>298.2544555664062</v>
+        <v>298.2543640136719</v>
       </c>
       <c r="C176" t="n">
         <v>325.5299987792969</v>
@@ -5047,7 +5059,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5076,11 +5088,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>325.2551879882812</v>
+        <v>325.2552185058594</v>
       </c>
       <c r="C178" t="n">
         <v>355</v>
@@ -5105,11 +5117,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>328.2853698730469</v>
+        <v>328.2852172851562</v>
       </c>
       <c r="C179" t="n">
         <v>357.6199951171875</v>
@@ -5134,7 +5146,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5163,11 +5175,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>354.9333801269531</v>
+        <v>354.9334106445312</v>
       </c>
       <c r="C181" t="n">
         <v>376.7799987792969</v>
@@ -5192,11 +5204,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>331.9952697753906</v>
+        <v>331.9953002929688</v>
       </c>
       <c r="C182" t="n">
         <v>352.4299926757812</v>
@@ -5221,7 +5233,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5250,11 +5262,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>332.6980285644531</v>
+        <v>332.697998046875</v>
       </c>
       <c r="C184" t="n">
         <v>352.4800109863281</v>
@@ -5279,11 +5291,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>351.9598083496094</v>
+        <v>351.959716796875</v>
       </c>
       <c r="C185" t="n">
         <v>372.0899963378906</v>
@@ -5308,11 +5320,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>357.805419921875</v>
+        <v>357.8053283691406</v>
       </c>
       <c r="C186" t="n">
         <v>378.2699890136719</v>
@@ -5337,11 +5349,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>374.2640075683594</v>
+        <v>374.2640380859375</v>
       </c>
       <c r="C187" t="n">
         <v>395.6700134277344</v>
@@ -5366,11 +5378,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>407.2338562011719</v>
+        <v>407.2339172363281</v>
       </c>
       <c r="C188" t="n">
         <v>429.7200012207031</v>
@@ -5395,11 +5407,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>431.6554260253906</v>
+        <v>431.6553344726562</v>
       </c>
       <c r="C189" t="n">
         <v>455.489990234375</v>
@@ -5424,7 +5436,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5453,11 +5465,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>466.5726013183594</v>
+        <v>466.5725402832031</v>
       </c>
       <c r="C191" t="n">
         <v>491.5400085449219</v>
@@ -5482,11 +5494,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>511.9826049804688</v>
+        <v>511.9825134277344</v>
       </c>
       <c r="C192" t="n">
         <v>539.3800048828125</v>
@@ -5511,11 +5523,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>538.8641357421875</v>
+        <v>538.8640747070312</v>
       </c>
       <c r="C193" t="n">
         <v>567.7000122070312</v>
@@ -5540,11 +5552,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>479.4722595214844</v>
+        <v>479.4723815917969</v>
       </c>
       <c r="C194" t="n">
         <v>505.1300048828125</v>
@@ -5569,11 +5581,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>493.6220703125</v>
+        <v>493.6220397949219</v>
       </c>
       <c r="C195" t="n">
         <v>519.25</v>
@@ -5598,11 +5610,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>547.4285888671875</v>
+        <v>547.4285278320312</v>
       </c>
       <c r="C196" t="n">
         <v>575.8499755859375</v>
@@ -5627,11 +5639,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>506.2989501953125</v>
+        <v>506.2990112304688</v>
       </c>
       <c r="C197" t="n">
         <v>531.719970703125</v>
@@ -5656,11 +5668,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>443.9304504394531</v>
+        <v>443.9305114746094</v>
       </c>
       <c r="C198" t="n">
         <v>466.2200012207031</v>
@@ -5685,11 +5697,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>456.3661804199219</v>
+        <v>456.3661499023438</v>
       </c>
       <c r="C199" t="n">
         <v>479.2799987792969</v>
@@ -5714,7 +5726,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5743,11 +5755,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>497.9969482421875</v>
+        <v>497.9969787597656</v>
       </c>
       <c r="C201" t="n">
         <v>522.0999755859375</v>
@@ -5772,11 +5784,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>450.4674682617188</v>
+        <v>450.4674987792969</v>
       </c>
       <c r="C202" t="n">
         <v>472.2699890136719</v>
@@ -5801,7 +5813,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5830,11 +5842,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>515.2838745117188</v>
+        <v>515.283935546875</v>
       </c>
       <c r="C204" t="n">
         <v>539.25</v>
@@ -5859,11 +5871,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>436.2115173339844</v>
+        <v>436.2114868164062</v>
       </c>
       <c r="C205" t="n">
         <v>456.5</v>
@@ -5888,11 +5900,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>488.4231262207031</v>
+        <v>488.4231872558594</v>
       </c>
       <c r="C206" t="n">
         <v>511.1400146484375</v>
@@ -5917,11 +5929,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>463.4667663574219</v>
+        <v>463.4667053222656</v>
       </c>
       <c r="C207" t="n">
         <v>484.1799926757812</v>
@@ -5946,11 +5958,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>475.6138916015625</v>
+        <v>475.6138000488281</v>
       </c>
       <c r="C208" t="n">
         <v>496.8699951171875</v>
@@ -5975,11 +5987,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>481.6922607421875</v>
+        <v>481.6921997070312</v>
       </c>
       <c r="C209" t="n">
         <v>503.2200012207031</v>
@@ -6004,11 +6016,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>490.6966857910156</v>
+        <v>490.6967163085938</v>
       </c>
       <c r="C210" t="n">
         <v>511.5599975585938</v>
@@ -6033,11 +6045,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>516.4228515625</v>
+        <v>516.4229125976562</v>
       </c>
       <c r="C211" t="n">
         <v>538.3800048828125</v>
@@ -6062,7 +6074,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6091,11 +6103,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>527.8739624023438</v>
+        <v>527.8739013671875</v>
       </c>
       <c r="C213" t="n">
         <v>549.280029296875</v>
@@ -6120,11 +6132,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>542.9428100585938</v>
+        <v>542.9429321289062</v>
       </c>
       <c r="C214" t="n">
         <v>564.9600219726562</v>
@@ -6149,11 +6161,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>530.9107666015625</v>
+        <v>530.910888671875</v>
       </c>
       <c r="C215" t="n">
         <v>552.4400024414062</v>
@@ -6178,11 +6190,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>570.6856689453125</v>
+        <v>570.685546875</v>
       </c>
       <c r="C216" t="n">
         <v>592.739990234375</v>
@@ -6207,7 +6219,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6236,11 +6248,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>684.2392578125</v>
+        <v>684.2391357421875</v>
       </c>
       <c r="C218" t="n">
         <v>694.8800048828125</v>
@@ -6265,11 +6277,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>733.575439453125</v>
+        <v>733.5753784179688</v>
       </c>
       <c r="C219" t="n">
         <v>743.8900146484375</v>
@@ -6294,7 +6306,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6323,11 +6335,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>714.0206909179688</v>
+        <v>714.020751953125</v>
       </c>
       <c r="C221" t="n">
         <v>722.9000244140625</v>
@@ -6352,7 +6364,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6381,11 +6393,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>839.5496826171875</v>
+        <v>839.5497436523438</v>
       </c>
       <c r="C223" t="n">
         <v>849.989990234375</v>
@@ -6410,7 +6422,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6439,11 +6451,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>882.6739501953125</v>
+        <v>882.673828125</v>
       </c>
       <c r="C225" t="n">
         <v>892.3800048828125</v>
@@ -6468,7 +6480,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6497,7 +6509,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6526,11 +6538,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>962.58642578125</v>
+        <v>962.5864868164062</v>
       </c>
       <c r="C228" t="n">
         <v>971.8800048828125</v>
@@ -6555,7 +6567,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6584,11 +6596,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>970.5099487304688</v>
+        <v>970.5100708007812</v>
       </c>
       <c r="C230" t="n">
         <v>979.8800048828125</v>
@@ -6613,7 +6625,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6642,7 +6654,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6671,7 +6683,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6700,7 +6712,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6729,7 +6741,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6758,7 +6770,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6787,7 +6799,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6816,7 +6828,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6845,11 +6857,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>907.4449462890625</v>
+        <v>907.4450073242188</v>
       </c>
       <c r="C239" t="n">
         <v>911.4500122070312</v>
@@ -6874,7 +6886,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6903,11 +6915,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>858.5507202148438</v>
+        <v>858.55078125</v>
       </c>
       <c r="C241" t="n">
         <v>862.3400268554688</v>
@@ -6932,7 +6944,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6961,7 +6973,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6990,7 +7002,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7019,7 +7031,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7048,7 +7060,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7077,7 +7089,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7106,7 +7118,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7135,7 +7147,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7164,32 +7176,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>904.7000122070312</v>
+        <v>896.47998046875</v>
       </c>
       <c r="C250" t="n">
-        <v>904.7000122070312</v>
+        <v>896.47998046875</v>
       </c>
       <c r="D250" t="n">
-        <v>35143100</v>
+        <v>38017400</v>
       </c>
       <c r="E250" t="n">
         <v>19.88</v>
       </c>
       <c r="F250" t="n">
-        <v>45.5080489037742</v>
+        <v>45.09456642196931</v>
       </c>
       <c r="G250" t="n">
         <v>443478804</v>
       </c>
       <c r="H250" t="n">
-        <v>401215279392.3596</v>
+        <v>397569869548.2246</v>
       </c>
       <c r="I250" t="n">
-        <v>0.07924414804726496</v>
+        <v>0.08572540481551402</v>
       </c>
     </row>
   </sheetData>
@@ -7221,75 +7233,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39692</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39775</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40165</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7325,13 +7337,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39776</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39859</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40254</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7367,13 +7379,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39852</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39943</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40339</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7409,13 +7421,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39944</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40055</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40469</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7442,7 +7454,7 @@
       <c r="I5" t="n">
         <v>2.479123858564118</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40469</v>
       </c>
       <c r="K5" t="n">
@@ -7455,13 +7467,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40056</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40139</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40165</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7488,7 +7500,7 @@
       <c r="I6" t="n">
         <v>2.479123858564118</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40469</v>
       </c>
       <c r="K6" t="n">
@@ -7501,13 +7513,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40140</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40223</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40254</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7534,7 +7546,7 @@
       <c r="I7" t="n">
         <v>2.599123858564118</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40469</v>
       </c>
       <c r="K7" t="n">
@@ -7547,13 +7559,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40217</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40307</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40339</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7580,7 +7592,7 @@
       <c r="I8" t="n">
         <v>2.799123858564118</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40469</v>
       </c>
       <c r="K8" t="n">
@@ -7593,13 +7605,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40308</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40419</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40469</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7626,7 +7638,7 @@
       <c r="I9" t="n">
         <v>2.918675022983609</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40469</v>
       </c>
       <c r="K9" t="n">
@@ -7639,13 +7651,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40420</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40503</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40529</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7672,7 +7684,7 @@
       <c r="I10" t="n">
         <v>3.028675022983609</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40529</v>
       </c>
       <c r="K10" t="n">
@@ -7685,13 +7697,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40504</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40587</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40619</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7718,7 +7730,7 @@
       <c r="I11" t="n">
         <v>3.148675022983609</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40619</v>
       </c>
       <c r="K11" t="n">
@@ -7731,13 +7743,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40588</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40671</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40703</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7764,7 +7776,7 @@
       <c r="I12" t="n">
         <v>3.198675022983609</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40703</v>
       </c>
       <c r="K12" t="n">
@@ -7777,13 +7789,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40672</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40783</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40830</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7810,7 +7822,7 @@
       <c r="I13" t="n">
         <v>3.3</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40830</v>
       </c>
       <c r="K13" t="n">
@@ -7823,13 +7835,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40784</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40867</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40893</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7856,7 +7868,7 @@
       <c r="I14" t="n">
         <v>3.32</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40893</v>
       </c>
       <c r="K14" t="n">
@@ -7869,13 +7881,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40868</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40951</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40983</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7902,7 +7914,7 @@
       <c r="I15" t="n">
         <v>3.43</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40983</v>
       </c>
       <c r="K15" t="n">
@@ -7915,13 +7927,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40952</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41035</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41066</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7948,7 +7960,7 @@
       <c r="I16" t="n">
         <v>3.58</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41066</v>
       </c>
       <c r="K16" t="n">
@@ -7961,13 +7973,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41036</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41154</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41201</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7994,7 +8006,7 @@
       <c r="I17" t="n">
         <v>3.890000000000001</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41201</v>
       </c>
       <c r="K17" t="n">
@@ -8007,13 +8019,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41155</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41238</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41264</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8040,7 +8052,7 @@
       <c r="I18" t="n">
         <v>4.11</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41264</v>
       </c>
       <c r="K18" t="n">
@@ -8053,13 +8065,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41239</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41322</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41353</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8086,7 +8098,7 @@
       <c r="I19" t="n">
         <v>4.45</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41353</v>
       </c>
       <c r="K19" t="n">
@@ -8099,13 +8111,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41323</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41406</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41436</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8132,7 +8144,7 @@
       <c r="I20" t="n">
         <v>4.61</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41436</v>
       </c>
       <c r="K20" t="n">
@@ -8145,13 +8157,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41407</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41518</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41563</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8178,7 +8190,7 @@
       <c r="I21" t="n">
         <v>4.63</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41563</v>
       </c>
       <c r="K21" t="n">
@@ -8191,13 +8203,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41519</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41602</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41628</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8224,7 +8236,7 @@
       <c r="I22" t="n">
         <v>4.64</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41628</v>
       </c>
       <c r="K22" t="n">
@@ -8237,13 +8249,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41603</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41686</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41712</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8270,7 +8282,7 @@
       <c r="I23" t="n">
         <v>4.449999999999999</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41712</v>
       </c>
       <c r="K23" t="n">
@@ -8283,13 +8295,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41687</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41770</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41795</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8316,7 +8328,7 @@
       <c r="I24" t="n">
         <v>4.48</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41795</v>
       </c>
       <c r="K24" t="n">
@@ -8329,13 +8341,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41771</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41882</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41927</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8362,7 +8374,7 @@
       <c r="I25" t="n">
         <v>4.65</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41927</v>
       </c>
       <c r="K25" t="n">
@@ -8375,13 +8387,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41883</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41966</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41991</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8408,7 +8420,7 @@
       <c r="I26" t="n">
         <v>4.81</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41991</v>
       </c>
       <c r="K26" t="n">
@@ -8421,13 +8433,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41967</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42050</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42074</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8454,7 +8466,7 @@
       <c r="I27" t="n">
         <v>5.11</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42074</v>
       </c>
       <c r="K27" t="n">
@@ -8467,13 +8479,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42051</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42134</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42159</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8500,7 +8512,7 @@
       <c r="I28" t="n">
         <v>5.21</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42159</v>
       </c>
       <c r="K28" t="n">
@@ -8513,13 +8525,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42135</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42246</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42291</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8546,7 +8558,7 @@
       <c r="I29" t="n">
         <v>5.37</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42291</v>
       </c>
       <c r="K29" t="n">
@@ -8559,13 +8571,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42247</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42330</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42356</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8592,7 +8604,7 @@
       <c r="I30" t="n">
         <v>5.34</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42356</v>
       </c>
       <c r="K30" t="n">
@@ -8605,13 +8617,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42331</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42414</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42438</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8638,7 +8650,7 @@
       <c r="I31" t="n">
         <v>5.23</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42438</v>
       </c>
       <c r="K31" t="n">
@@ -8651,13 +8663,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42415</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42498</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8684,7 +8696,7 @@
       <c r="I32" t="n">
         <v>5.300000000000001</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="K32" t="n">
@@ -8697,13 +8709,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42499</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42610</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42655</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8730,7 +8742,7 @@
       <c r="I33" t="n">
         <v>5.33</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42655</v>
       </c>
       <c r="K33" t="n">
@@ -8743,13 +8755,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42611</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42694</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42720</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8776,7 +8788,7 @@
       <c r="I34" t="n">
         <v>5.48</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42720</v>
       </c>
       <c r="K34" t="n">
@@ -8789,13 +8801,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42695</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42778</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42803</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8822,7 +8834,7 @@
       <c r="I35" t="n">
         <v>5.409999999999999</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42803</v>
       </c>
       <c r="K35" t="n">
@@ -8835,13 +8847,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42779</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42862</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8868,7 +8880,7 @@
       <c r="I36" t="n">
         <v>5.76</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="K36" t="n">
@@ -8881,13 +8893,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42863</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42981</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43026</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8914,7 +8926,7 @@
       <c r="I37" t="n">
         <v>6.08</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43026</v>
       </c>
       <c r="K37" t="n">
@@ -8927,13 +8939,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42982</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43065</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43090</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8960,7 +8972,7 @@
       <c r="I38" t="n">
         <v>6.29</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43090</v>
       </c>
       <c r="K38" t="n">
@@ -8973,13 +8985,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43066</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43149</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43174</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9006,7 +9018,7 @@
       <c r="I39" t="n">
         <v>6.71</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43174</v>
       </c>
       <c r="K39" t="n">
@@ -9019,13 +9031,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43150</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43233</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43258</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9052,7 +9064,7 @@
       <c r="I40" t="n">
         <v>6.82</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43258</v>
       </c>
       <c r="K40" t="n">
@@ -9065,13 +9077,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43234</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43345</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9098,7 +9110,7 @@
       <c r="I41" t="n">
         <v>7.09</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="K41" t="n">
@@ -9111,13 +9123,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43346</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43429</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43454</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9144,7 +9156,7 @@
       <c r="I42" t="n">
         <v>7.369999999999999</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43454</v>
       </c>
       <c r="K42" t="n">
@@ -9157,13 +9169,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43430</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43513</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43537</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9190,7 +9202,7 @@
       <c r="I43" t="n">
         <v>7.789999999999999</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43537</v>
       </c>
       <c r="K43" t="n">
@@ -9203,13 +9215,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43514</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43597</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43622</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9236,7 +9248,7 @@
       <c r="I44" t="n">
         <v>8.139999999999999</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43622</v>
       </c>
       <c r="K44" t="n">
@@ -9249,13 +9261,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43598</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43709</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43749</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9282,7 +9294,7 @@
       <c r="I45" t="n">
         <v>8.26</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43749</v>
       </c>
       <c r="K45" t="n">
@@ -9295,13 +9307,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43710</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43793</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43822</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9328,7 +9340,7 @@
       <c r="I46" t="n">
         <v>8.43</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43822</v>
       </c>
       <c r="K46" t="n">
@@ -9341,13 +9353,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43794</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43877</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43902</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9374,7 +9386,7 @@
       <c r="I47" t="n">
         <v>8.52</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43902</v>
       </c>
       <c r="K47" t="n">
@@ -9387,13 +9399,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43878</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43961</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43986</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9420,7 +9432,7 @@
       <c r="I48" t="n">
         <v>8.360000000000001</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43986</v>
       </c>
       <c r="K48" t="n">
@@ -9433,13 +9445,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43962</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44073</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44111</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9466,7 +9478,7 @@
       <c r="I49" t="n">
         <v>9.02</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44111</v>
       </c>
       <c r="K49" t="n">
@@ -9479,13 +9491,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44074</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44157</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44181</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9512,7 +9524,7 @@
       <c r="I50" t="n">
         <v>9.74</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44181</v>
       </c>
       <c r="K50" t="n">
@@ -9525,13 +9537,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44158</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44241</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44265</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9558,7 +9570,7 @@
       <c r="I51" t="n">
         <v>9.780000000000001</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44265</v>
       </c>
       <c r="K51" t="n">
@@ -9571,13 +9583,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44242</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44325</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44350</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9604,7 +9616,7 @@
       <c r="I52" t="n">
         <v>10.64</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44350</v>
       </c>
       <c r="K52" t="n">
@@ -9617,13 +9629,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44326</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44437</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44475</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9650,7 +9662,7 @@
       <c r="I53" t="n">
         <v>11.27</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44475</v>
       </c>
       <c r="K53" t="n">
@@ -9663,13 +9675,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44438</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44521</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44552</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9696,7 +9708,7 @@
       <c r="I54" t="n">
         <v>11.63</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44552</v>
       </c>
       <c r="K54" t="n">
@@ -9709,13 +9721,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44522</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44605</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44630</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9742,7 +9754,7 @@
       <c r="I55" t="n">
         <v>12.41</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44630</v>
       </c>
       <c r="K55" t="n">
@@ -9755,13 +9767,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44606</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44689</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44714</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9788,7 +9800,7 @@
       <c r="I56" t="n">
         <v>12.7</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44714</v>
       </c>
       <c r="K56" t="n">
@@ -9801,13 +9813,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44690</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44801</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44839</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9834,7 +9846,7 @@
       <c r="I57" t="n">
         <v>13.14</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44839</v>
       </c>
       <c r="K57" t="n">
@@ -9847,13 +9859,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44802</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44885</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44924</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9880,7 +9892,7 @@
       <c r="I58" t="n">
         <v>13.23</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44924</v>
       </c>
       <c r="K58" t="n">
@@ -9893,13 +9905,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44886</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44969</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44994</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9926,7 +9938,7 @@
       <c r="I59" t="n">
         <v>13.61</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44994</v>
       </c>
       <c r="K59" t="n">
@@ -9939,13 +9951,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44970</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45053</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9972,7 +9984,7 @@
       <c r="I60" t="n">
         <v>13.5</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="K60" t="n">
@@ -9985,13 +9997,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45054</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45172</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45210</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10018,7 +10030,7 @@
       <c r="I61" t="n">
         <v>14.16</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45210</v>
       </c>
       <c r="K61" t="n">
@@ -10031,13 +10043,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45173</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45256</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45280</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10064,7 +10076,7 @@
       <c r="I62" t="n">
         <v>14.67</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45280</v>
       </c>
       <c r="K62" t="n">
@@ -10077,13 +10089,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45257</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45340</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45364</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10110,7 +10122,7 @@
       <c r="I63" t="n">
         <v>15.29</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45364</v>
       </c>
       <c r="K63" t="n">
@@ -10123,13 +10135,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45341</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45424</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45449</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10156,7 +10168,7 @@
       <c r="I64" t="n">
         <v>16.14</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45449</v>
       </c>
       <c r="K64" t="n">
@@ -10169,13 +10181,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45425</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45536</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45574</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10202,7 +10214,7 @@
       <c r="I65" t="n">
         <v>16.56</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45574</v>
       </c>
       <c r="K65" t="n">
@@ -10215,13 +10227,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45537</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45620</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45645</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10248,7 +10260,7 @@
       <c r="I66" t="n">
         <v>17.02</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45645</v>
       </c>
       <c r="K66" t="n">
@@ -10261,13 +10273,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45621</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45704</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45729</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10294,7 +10306,7 @@
       <c r="I67" t="n">
         <v>17.12</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45729</v>
       </c>
       <c r="K67" t="n">
@@ -10307,13 +10319,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45705</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45788</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10340,7 +10352,7 @@
       <c r="I68" t="n">
         <v>17.62</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="K68" t="n">
@@ -10353,13 +10365,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45789</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45900</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45938</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10386,7 +10398,7 @@
       <c r="I69" t="n">
         <v>18.21</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45938</v>
       </c>
       <c r="K69" t="n">
@@ -10399,13 +10411,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45901</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45984</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46008</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10432,7 +10444,7 @@
       <c r="I70" t="n">
         <v>18.67</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46008</v>
       </c>
       <c r="K70" t="n">
@@ -10445,13 +10457,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45985</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46068</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46092</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10478,7 +10490,7 @@
       <c r="I71" t="n">
         <v>19.23</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46092</v>
       </c>
       <c r="K71" t="n">
@@ -10491,13 +10503,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46152</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46176</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10524,7 +10536,7 @@
       <c r="I72" t="n">
         <v>19.88</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46176</v>
       </c>
       <c r="K72" t="n">
@@ -10537,13 +10549,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46083</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46173</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46218</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10597,52 +10609,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40158</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40165</v>
       </c>
       <c r="C2" t="n">
@@ -10671,10 +10683,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40242</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40254</v>
       </c>
       <c r="C3" t="n">
@@ -10703,10 +10715,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40326</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40339</v>
       </c>
       <c r="C4" t="n">
@@ -10735,10 +10747,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40469</v>
       </c>
       <c r="C5" t="n">
@@ -10767,10 +10779,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40522</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40529</v>
       </c>
       <c r="C6" t="n">
@@ -10799,10 +10811,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40606</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40619</v>
       </c>
       <c r="C7" t="n">
@@ -10831,10 +10843,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40690</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40703</v>
       </c>
       <c r="C8" t="n">
@@ -10863,10 +10875,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40830</v>
       </c>
       <c r="C9" t="n">
@@ -10895,10 +10907,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40886</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40893</v>
       </c>
       <c r="C10" t="n">
@@ -10927,10 +10939,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40977</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40983</v>
       </c>
       <c r="C11" t="n">
@@ -10959,10 +10971,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41060</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41066</v>
       </c>
       <c r="C12" t="n">
@@ -10991,10 +11003,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41187</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41201</v>
       </c>
       <c r="C13" t="n">
@@ -11023,10 +11035,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41257</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41264</v>
       </c>
       <c r="C14" t="n">
@@ -11055,10 +11067,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41346</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41353</v>
       </c>
       <c r="C15" t="n">
@@ -11087,10 +11099,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41429</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41436</v>
       </c>
       <c r="C16" t="n">
@@ -11119,10 +11131,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41556</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41563</v>
       </c>
       <c r="C17" t="n">
@@ -11151,10 +11163,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41621</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41628</v>
       </c>
       <c r="C18" t="n">
@@ -11183,10 +11195,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41705</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41712</v>
       </c>
       <c r="C19" t="n">
@@ -11215,10 +11227,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41787</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41795</v>
       </c>
       <c r="C20" t="n">
@@ -11247,10 +11259,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41920</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41927</v>
       </c>
       <c r="C21" t="n">
@@ -11279,10 +11291,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41984</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41991</v>
       </c>
       <c r="C22" t="n">
@@ -11311,10 +11323,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42067</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42074</v>
       </c>
       <c r="C23" t="n">
@@ -11343,10 +11355,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42151</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42159</v>
       </c>
       <c r="C24" t="n">
@@ -11375,10 +11387,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42282</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42291</v>
       </c>
       <c r="C25" t="n">
@@ -11407,10 +11419,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42348</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42356</v>
       </c>
       <c r="C26" t="n">
@@ -11439,10 +11451,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42431</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42438</v>
       </c>
       <c r="C27" t="n">
@@ -11471,10 +11483,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42515</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42522</v>
       </c>
       <c r="C28" t="n">
@@ -11503,10 +11515,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42647</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42655</v>
       </c>
       <c r="C29" t="n">
@@ -11535,10 +11547,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42712</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42720</v>
       </c>
       <c r="C30" t="n">
@@ -11567,10 +11579,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42795</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42803</v>
       </c>
       <c r="C31" t="n">
@@ -11599,10 +11611,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42879</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42887</v>
       </c>
       <c r="C32" t="n">
@@ -11631,10 +11643,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43018</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43026</v>
       </c>
       <c r="C33" t="n">
@@ -11663,10 +11675,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43082</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43090</v>
       </c>
       <c r="C34" t="n">
@@ -11695,10 +11707,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43166</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43174</v>
       </c>
       <c r="C35" t="n">
@@ -11727,10 +11739,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43250</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43258</v>
       </c>
       <c r="C36" t="n">
@@ -11759,10 +11771,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43391</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="C37" t="n">
@@ -11791,10 +11803,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43446</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43454</v>
       </c>
       <c r="C38" t="n">
@@ -11823,10 +11835,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43530</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43537</v>
       </c>
       <c r="C39" t="n">
@@ -11855,10 +11867,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43614</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43622</v>
       </c>
       <c r="C40" t="n">
@@ -11887,10 +11899,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43741</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43749</v>
       </c>
       <c r="C41" t="n">
@@ -11919,10 +11931,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43810</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43822</v>
       </c>
       <c r="C42" t="n">
@@ -11951,10 +11963,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43894</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43902</v>
       </c>
       <c r="C43" t="n">
@@ -11983,10 +11995,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43978</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43986</v>
       </c>
       <c r="C44" t="n">
@@ -12015,10 +12027,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44103</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44111</v>
       </c>
       <c r="C45" t="n">
@@ -12047,10 +12059,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44174</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44181</v>
       </c>
       <c r="C46" t="n">
@@ -12079,10 +12091,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44258</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44265</v>
       </c>
       <c r="C47" t="n">
@@ -12111,10 +12123,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44342</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44350</v>
       </c>
       <c r="C48" t="n">
@@ -12143,10 +12155,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44467</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44475</v>
       </c>
       <c r="C49" t="n">
@@ -12175,10 +12187,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44544</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44552</v>
       </c>
       <c r="C50" t="n">
@@ -12207,10 +12219,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44622</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44630</v>
       </c>
       <c r="C51" t="n">
@@ -12239,10 +12251,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44706</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44714</v>
       </c>
       <c r="C52" t="n">
@@ -12271,10 +12283,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44831</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44839</v>
       </c>
       <c r="C53" t="n">
@@ -12303,10 +12315,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44917</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44924</v>
       </c>
       <c r="C54" t="n">
@@ -12335,10 +12347,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44986</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44994</v>
       </c>
       <c r="C55" t="n">
@@ -12367,10 +12379,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45070</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="C56" t="n">
@@ -12399,10 +12411,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45202</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45210</v>
       </c>
       <c r="C57" t="n">
@@ -12431,10 +12443,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45273</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45280</v>
       </c>
       <c r="C58" t="n">
@@ -12463,10 +12475,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45357</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45364</v>
       </c>
       <c r="C59" t="n">
@@ -12495,10 +12507,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45441</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45449</v>
       </c>
       <c r="C60" t="n">
@@ -12527,10 +12539,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45574</v>
       </c>
       <c r="C61" t="n">
@@ -12559,10 +12571,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45637</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45645</v>
       </c>
       <c r="C62" t="n">
@@ -12591,10 +12603,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45721</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45729</v>
       </c>
       <c r="C63" t="n">
@@ -12623,10 +12635,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45805</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45813</v>
       </c>
       <c r="C64" t="n">
@@ -12655,10 +12667,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45938</v>
       </c>
       <c r="C65" t="n">
@@ -12687,10 +12699,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46001</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>46008</v>
       </c>
       <c r="C66" t="n">
@@ -12719,10 +12731,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46085</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46092</v>
       </c>
       <c r="C67" t="n">
@@ -12751,10 +12763,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46169</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46176</v>
       </c>
       <c r="C68" t="n">
@@ -12801,12 +12813,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/COST.xlsx
+++ b/salidas/empresas/COST.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>33.7513542175293</v>
+        <v>33.75135803222656</v>
       </c>
       <c r="C2" t="n">
         <v>49.88999938964844</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>34.71184158325195</v>
+        <v>34.71185684204102</v>
       </c>
       <c r="C3" t="n">
         <v>51.18999862670898</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>36.72581100463867</v>
+        <v>36.72582626342773</v>
       </c>
       <c r="C4" t="n">
         <v>54.15999984741211</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>36.90888977050781</v>
+        <v>36.90889358520508</v>
       </c>
       <c r="C5" t="n">
         <v>54.43000030517578</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>35.97422790527344</v>
+        <v>35.97422409057617</v>
       </c>
       <c r="C6" t="n">
         <v>52.93000030517578</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>35.94950485229492</v>
+        <v>35.94950866699219</v>
       </c>
       <c r="C8" t="n">
         <v>52.7599983215332</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>31.88167762756348</v>
+        <v>31.8816967010498</v>
       </c>
       <c r="C9" t="n">
         <v>46.79000091552734</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>33.85087585449219</v>
+        <v>33.85086441040039</v>
       </c>
       <c r="C10" t="n">
         <v>49.68000030517578</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>36.37196731567383</v>
+        <v>36.3719596862793</v>
       </c>
       <c r="C11" t="n">
         <v>53.38000106811523</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>35.72465896606445</v>
+        <v>35.72465133666992</v>
       </c>
       <c r="C12" t="n">
         <v>52.29999923706055</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>36.11402130126953</v>
+        <v>36.11400985717773</v>
       </c>
       <c r="C13" t="n">
         <v>52.86999893188477</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>38.36131286621094</v>
+        <v>38.36133193969727</v>
       </c>
       <c r="C14" t="n">
         <v>56.15999984741211</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>36.8621940612793</v>
+        <v>36.86217880249023</v>
       </c>
       <c r="C16" t="n">
         <v>53.84000015258789</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>36.77563095092773</v>
+        <v>36.7756233215332</v>
       </c>
       <c r="C17" t="n">
         <v>53.56999969482422</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>38.7664680480957</v>
+        <v>38.76647186279297</v>
       </c>
       <c r="C18" t="n">
         <v>56.47000122070312</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>41.15170669555664</v>
+        <v>41.15170288085938</v>
       </c>
       <c r="C20" t="n">
         <v>59.79999923706055</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>42.49361038208008</v>
+        <v>42.49359893798828</v>
       </c>
       <c r="C21" t="n">
         <v>61.75</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>42.23208999633789</v>
+        <v>42.23210144042969</v>
       </c>
       <c r="C22" t="n">
         <v>61.36999893188477</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>46.28533554077148</v>
+        <v>46.28533935546875</v>
       </c>
       <c r="C23" t="n">
         <v>67.26000213623047</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>46.48387908935547</v>
+        <v>46.48389434814453</v>
       </c>
       <c r="C24" t="n">
         <v>67.40000152587891</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>48.11151123046875</v>
+        <v>48.11150741577148</v>
       </c>
       <c r="C25" t="n">
         <v>69.76000213623047</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>42.80083847045898</v>
+        <v>42.80083465576172</v>
       </c>
       <c r="C27" t="n">
         <v>61.91999816894531</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>44.90909194946289</v>
+        <v>44.90907287597656</v>
       </c>
       <c r="C28" t="n">
         <v>64.97000122070312</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>49.25</v>
+        <v>49.25000381469727</v>
       </c>
       <c r="C29" t="n">
         <v>71.25</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>49.40524673461914</v>
+        <v>49.40524291992188</v>
       </c>
       <c r="C30" t="n">
         <v>71.31999969482422</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>48.58781814575195</v>
+        <v>48.58781051635742</v>
       </c>
       <c r="C31" t="n">
         <v>70.13999938964844</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>43.42007827758789</v>
+        <v>43.42006683349609</v>
       </c>
       <c r="C32" t="n">
         <v>62.68000030517578</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>46.56951522827148</v>
+        <v>46.56951141357422</v>
       </c>
       <c r="C33" t="n">
         <v>67.05999755859375</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>45.0903434753418</v>
+        <v>45.09035110473633</v>
       </c>
       <c r="C34" t="n">
         <v>64.93000030517578</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>39.59035110473633</v>
+        <v>39.59032440185547</v>
       </c>
       <c r="C35" t="n">
         <v>57.0099983215332</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>36.57030487060547</v>
+        <v>36.5703010559082</v>
       </c>
       <c r="C37" t="n">
         <v>52.5</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>31.36686706542969</v>
+        <v>31.36688041687012</v>
       </c>
       <c r="C38" t="n">
         <v>45.02999877929688</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>29.60079765319824</v>
+        <v>29.60079574584961</v>
       </c>
       <c r="C39" t="n">
         <v>42.34000015258789</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>32.38330459594727</v>
+        <v>32.3833122253418</v>
       </c>
       <c r="C40" t="n">
         <v>46.31999969482422</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>33.9772834777832</v>
+        <v>33.97729110717773</v>
       </c>
       <c r="C41" t="n">
         <v>48.59999847412109</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>34.05202865600586</v>
+        <v>34.05201721191406</v>
       </c>
       <c r="C42" t="n">
         <v>48.52000045776367</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>32.12904739379883</v>
+        <v>32.12906265258789</v>
       </c>
       <c r="C43" t="n">
         <v>45.77999877929688</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>34.73979187011719</v>
+        <v>34.73980331420898</v>
       </c>
       <c r="C44" t="n">
         <v>49.5</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>35.91061019897461</v>
+        <v>35.91062927246094</v>
       </c>
       <c r="C45" t="n">
         <v>50.97999954223633</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>39.71441650390625</v>
+        <v>39.71440505981445</v>
       </c>
       <c r="C46" t="n">
         <v>56.38000106811523</v>
@@ -1372,7 +1372,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>42.32990264892578</v>
+        <v>42.32992172241211</v>
       </c>
       <c r="C48" t="n">
         <v>59.90999984741211</v>
@@ -1391,7 +1391,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>41.80706405639648</v>
+        <v>41.80704879760742</v>
       </c>
       <c r="C49" t="n">
         <v>59.16999816894531</v>
@@ -1416,7 +1416,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>40.57765579223633</v>
+        <v>40.57764053344727</v>
       </c>
       <c r="C50" t="n">
         <v>57.43000030517578</v>
@@ -1441,7 +1441,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>43.21122741699219</v>
+        <v>43.21123504638672</v>
       </c>
       <c r="C51" t="n">
         <v>60.97000122070312</v>
@@ -1466,7 +1466,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>42.31822204589844</v>
+        <v>42.31824493408203</v>
       </c>
       <c r="C52" t="n">
         <v>59.70999908447266</v>
@@ -1491,7 +1491,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>41.87173080444336</v>
+        <v>41.87175369262695</v>
       </c>
       <c r="C53" t="n">
         <v>59.08000183105469</v>
@@ -1516,7 +1516,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>41.42530822753906</v>
+        <v>41.42532348632812</v>
       </c>
       <c r="C54" t="n">
         <v>58.25</v>
@@ -1541,7 +1541,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>38.99311447143555</v>
+        <v>38.99313354492188</v>
       </c>
       <c r="C55" t="n">
         <v>54.83000183105469</v>
@@ -1566,7 +1566,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>40.33012390136719</v>
+        <v>40.33011627197266</v>
       </c>
       <c r="C56" t="n">
         <v>56.70999908447266</v>
@@ -1591,7 +1591,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>40.32695007324219</v>
+        <v>40.32694625854492</v>
       </c>
       <c r="C57" t="n">
         <v>56.5</v>
@@ -1616,7 +1616,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>46.02982711791992</v>
+        <v>46.02983093261719</v>
       </c>
       <c r="C58" t="n">
         <v>64.48999786376953</v>
@@ -1641,7 +1641,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>44.94686889648438</v>
+        <v>44.94687271118164</v>
       </c>
       <c r="C59" t="n">
         <v>62.77000045776367</v>
@@ -1670,7 +1670,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>48.41259384155273</v>
+        <v>48.41260147094727</v>
       </c>
       <c r="C60" t="n">
         <v>67.61000061035156</v>
@@ -1699,7 +1699,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>51.70645523071289</v>
+        <v>51.70645904541016</v>
       </c>
       <c r="C61" t="n">
         <v>72.20999908447266</v>
@@ -1757,7 +1757,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>53.70106506347656</v>
+        <v>53.70105743408203</v>
       </c>
       <c r="C63" t="n">
         <v>74.79000091552734</v>
@@ -1786,7 +1786,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>52.64556884765625</v>
+        <v>52.64554977416992</v>
       </c>
       <c r="C64" t="n">
         <v>73.31999969482422</v>
@@ -1815,7 +1815,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>58.08102035522461</v>
+        <v>58.08100891113281</v>
       </c>
       <c r="C65" t="n">
         <v>80.88999938964844</v>
@@ -1844,7 +1844,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>59.39602279663086</v>
+        <v>59.3960075378418</v>
       </c>
       <c r="C66" t="n">
         <v>82.48000335693359</v>
@@ -1873,7 +1873,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>58.5030517578125</v>
+        <v>58.50307846069336</v>
       </c>
       <c r="C67" t="n">
         <v>81.23999786376953</v>
@@ -1902,7 +1902,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>56.34987640380859</v>
+        <v>56.34988403320312</v>
       </c>
       <c r="C68" t="n">
         <v>78.25</v>
@@ -1931,7 +1931,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>56.73828887939453</v>
+        <v>56.73829650878906</v>
       </c>
       <c r="C69" t="n">
         <v>78.54000091552734</v>
@@ -1960,7 +1960,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>59.33174133300781</v>
+        <v>59.33174514770508</v>
       </c>
       <c r="C70" t="n">
         <v>82.12999725341797</v>
@@ -1989,7 +1989,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>60.14086532592773</v>
+        <v>60.1408576965332</v>
       </c>
       <c r="C71" t="n">
         <v>83.25</v>
@@ -2047,7 +2047,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>60.36356735229492</v>
+        <v>60.36358642578125</v>
       </c>
       <c r="C73" t="n">
         <v>83.31999969482422</v>
@@ -2076,7 +2076,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>59.60287094116211</v>
+        <v>59.60287475585938</v>
       </c>
       <c r="C74" t="n">
         <v>82.26999664306641</v>
@@ -2105,7 +2105,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>62.52610778808594</v>
+        <v>62.52607345581055</v>
       </c>
       <c r="C75" t="n">
         <v>86.05999755859375</v>
@@ -2134,7 +2134,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>65.96990203857422</v>
+        <v>65.96990966796875</v>
       </c>
       <c r="C76" t="n">
         <v>90.80000305175781</v>
@@ -2163,7 +2163,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>64.06636047363281</v>
+        <v>64.06637573242188</v>
       </c>
       <c r="C77" t="n">
         <v>88.18000030517578</v>
@@ -2192,7 +2192,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>62.97356796264648</v>
+        <v>62.97353744506836</v>
       </c>
       <c r="C78" t="n">
         <v>86.38999938964844</v>
@@ -2221,7 +2221,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>69.249755859375</v>
+        <v>69.24978637695312</v>
       </c>
       <c r="C79" t="n">
         <v>95</v>
@@ -2250,7 +2250,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>70.10994720458984</v>
+        <v>70.10991668701172</v>
       </c>
       <c r="C80" t="n">
         <v>96.18000030517578</v>
@@ -2279,7 +2279,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>71.54723358154297</v>
+        <v>71.54725646972656</v>
       </c>
       <c r="C81" t="n">
         <v>97.87000274658203</v>
@@ -2308,7 +2308,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>73.22129821777344</v>
+        <v>73.22129058837891</v>
       </c>
       <c r="C82" t="n">
         <v>100.1600036621094</v>
@@ -2337,7 +2337,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>71.95658874511719</v>
+        <v>71.95661926269531</v>
       </c>
       <c r="C83" t="n">
         <v>98.43000030517578</v>
@@ -2366,7 +2366,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>76.18898010253906</v>
+        <v>76.18901062011719</v>
       </c>
       <c r="C84" t="n">
         <v>103.9199981689453</v>
@@ -2395,7 +2395,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>77.50460815429688</v>
+        <v>77.50457000732422</v>
       </c>
       <c r="C85" t="n">
         <v>98.73000335693359</v>
@@ -2424,7 +2424,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>80.33848571777344</v>
+        <v>80.33846282958984</v>
       </c>
       <c r="C86" t="n">
         <v>102.3399963378906</v>
@@ -2453,7 +2453,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>79.7264404296875</v>
+        <v>79.72643280029297</v>
       </c>
       <c r="C87" t="n">
         <v>101.2900009155273</v>
@@ -2482,7 +2482,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>83.52032470703125</v>
+        <v>83.52034759521484</v>
       </c>
       <c r="C88" t="n">
         <v>106.1100006103516</v>
@@ -2511,7 +2511,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>85.34639739990234</v>
+        <v>85.34641265869141</v>
       </c>
       <c r="C89" t="n">
         <v>108.4300003051758</v>
@@ -2540,7 +2540,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>86.53177642822266</v>
+        <v>86.53173828125</v>
       </c>
       <c r="C90" t="n">
         <v>109.629997253418</v>
@@ -2569,7 +2569,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>87.27370452880859</v>
+        <v>87.27372741699219</v>
       </c>
       <c r="C91" t="n">
         <v>110.5699996948242</v>
@@ -2598,7 +2598,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>92.68046569824219</v>
+        <v>92.68049621582031</v>
       </c>
       <c r="C92" t="n">
         <v>117.4199981689453</v>
@@ -2627,7 +2627,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>88.52947998046875</v>
+        <v>88.52947235107422</v>
       </c>
       <c r="C93" t="n">
         <v>111.870002746582</v>
@@ -2656,7 +2656,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>91.14096069335938</v>
+        <v>91.14096832275391</v>
       </c>
       <c r="C94" t="n">
         <v>115.1699981689453</v>
@@ -2685,7 +2685,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>93.38050842285156</v>
+        <v>93.38052368164062</v>
       </c>
       <c r="C95" t="n">
         <v>118</v>
@@ -2714,7 +2714,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>99.51224517822266</v>
+        <v>99.51226043701172</v>
       </c>
       <c r="C96" t="n">
         <v>125.4300003051758</v>
@@ -2743,7 +2743,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>94.4267578125</v>
+        <v>94.42672729492188</v>
       </c>
       <c r="C97" t="n">
         <v>119.0199966430664</v>
@@ -2772,7 +2772,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>89.14291381835938</v>
+        <v>89.14288330078125</v>
       </c>
       <c r="C98" t="n">
         <v>112.3600006103516</v>
@@ -2801,7 +2801,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>92.91596984863281</v>
+        <v>92.91594696044922</v>
       </c>
       <c r="C99" t="n">
         <v>116.8000030517578</v>
@@ -2859,7 +2859,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>92.02500152587891</v>
+        <v>92.02499389648438</v>
       </c>
       <c r="C101" t="n">
         <v>115.6800003051758</v>
@@ -2888,7 +2888,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>92.57810974121094</v>
+        <v>92.57807922363281</v>
       </c>
       <c r="C102" t="n">
         <v>116.0199966430664</v>
@@ -2917,7 +2917,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>91.89183807373047</v>
+        <v>91.89185333251953</v>
       </c>
       <c r="C103" t="n">
         <v>115.1600036621094</v>
@@ -2946,7 +2946,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>94.07529449462891</v>
+        <v>94.07530212402344</v>
       </c>
       <c r="C104" t="n">
         <v>117.5400009155273</v>
@@ -3033,7 +3033,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>106.7450942993164</v>
+        <v>106.7451248168945</v>
       </c>
       <c r="C107" t="n">
         <v>133.3699951171875</v>
@@ -3062,7 +3062,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>114.0437545776367</v>
+        <v>114.0437240600586</v>
       </c>
       <c r="C108" t="n">
         <v>142.1199951171875</v>
@@ -3091,7 +3091,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>113.7468490600586</v>
+        <v>113.7468032836914</v>
       </c>
       <c r="C109" t="n">
         <v>141.75</v>
@@ -3120,7 +3120,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>114.7418670654297</v>
+        <v>114.7419204711914</v>
       </c>
       <c r="C110" t="n">
         <v>142.9900054931641</v>
@@ -3149,7 +3149,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>122.1270523071289</v>
+        <v>122.1270370483398</v>
       </c>
       <c r="C111" t="n">
         <v>146.9600067138672</v>
@@ -3178,7 +3178,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>125.8999176025391</v>
+        <v>125.8999099731445</v>
       </c>
       <c r="C112" t="n">
         <v>151.5</v>
@@ -3207,7 +3207,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>119.2029495239258</v>
+        <v>119.2029800415039</v>
       </c>
       <c r="C113" t="n">
         <v>143.0500030517578</v>
@@ -3236,7 +3236,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>118.8196334838867</v>
+        <v>118.8196716308594</v>
       </c>
       <c r="C114" t="n">
         <v>142.5899963378906</v>
@@ -3294,7 +3294,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>121.0778961181641</v>
+        <v>121.0779037475586</v>
       </c>
       <c r="C116" t="n">
         <v>145.3000030517578</v>
@@ -3323,7 +3323,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>117.0239410400391</v>
+        <v>117.0239562988281</v>
       </c>
       <c r="C117" t="n">
         <v>140.0500030517578</v>
@@ -3352,7 +3352,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>120.8008117675781</v>
+        <v>120.8008041381836</v>
       </c>
       <c r="C118" t="n">
         <v>144.5700073242188</v>
@@ -3381,7 +3381,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>132.1230163574219</v>
+        <v>132.1230010986328</v>
       </c>
       <c r="C119" t="n">
         <v>158.1199951171875</v>
@@ -3439,7 +3439,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>135.2960357666016</v>
+        <v>135.2960662841797</v>
       </c>
       <c r="C121" t="n">
         <v>161.5</v>
@@ -3468,7 +3468,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>126.6002349853516</v>
+        <v>126.6002578735352</v>
       </c>
       <c r="C122" t="n">
         <v>151.1199951171875</v>
@@ -3497,7 +3497,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>126.0278701782227</v>
+        <v>126.0278930664062</v>
       </c>
       <c r="C123" t="n">
         <v>150.0299987792969</v>
@@ -3526,7 +3526,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>132.3700561523438</v>
+        <v>132.3700408935547</v>
       </c>
       <c r="C124" t="n">
         <v>157.5800018310547</v>
@@ -3555,7 +3555,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>124.7998886108398</v>
+        <v>124.7998428344727</v>
       </c>
       <c r="C125" t="n">
         <v>148.1300048828125</v>
@@ -3584,7 +3584,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>125.3390579223633</v>
+        <v>125.3389663696289</v>
       </c>
       <c r="C126" t="n">
         <v>148.7700042724609</v>
@@ -3613,7 +3613,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>132.3065643310547</v>
+        <v>132.3065795898438</v>
       </c>
       <c r="C127" t="n">
         <v>157.0399932861328</v>
@@ -3642,7 +3642,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>140.8832244873047</v>
+        <v>140.8832397460938</v>
       </c>
       <c r="C128" t="n">
         <v>167.2200012207031</v>
@@ -3671,7 +3671,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>136.9282531738281</v>
+        <v>136.9283142089844</v>
       </c>
       <c r="C129" t="n">
         <v>162.0899963378906</v>
@@ -3729,7 +3729,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>124.9156723022461</v>
+        <v>124.9156799316406</v>
       </c>
       <c r="C131" t="n">
         <v>147.8699951171875</v>
@@ -3758,7 +3758,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>127.1982421875</v>
+        <v>127.1982574462891</v>
       </c>
       <c r="C132" t="n">
         <v>150.1100006103516</v>
@@ -3787,7 +3787,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>135.671875</v>
+        <v>135.6718902587891</v>
       </c>
       <c r="C133" t="n">
         <v>160.1100006103516</v>
@@ -3816,7 +3816,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>138.9258270263672</v>
+        <v>138.9257965087891</v>
       </c>
       <c r="C134" t="n">
         <v>163.9499969482422</v>
@@ -3845,7 +3845,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>150.5408325195312</v>
+        <v>150.5408020019531</v>
       </c>
       <c r="C135" t="n">
         <v>177.1799926757812</v>
@@ -3903,7 +3903,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>150.8297729492188</v>
+        <v>150.8296661376953</v>
       </c>
       <c r="C137" t="n">
         <v>177.5200042724609</v>
@@ -3932,7 +3932,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>159.9612731933594</v>
+        <v>159.961181640625</v>
       </c>
       <c r="C138" t="n">
         <v>180.4299926757812</v>
@@ -3961,7 +3961,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>141.7868194580078</v>
+        <v>141.786865234375</v>
       </c>
       <c r="C139" t="n">
         <v>159.9299926757812</v>
@@ -3990,7 +3990,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>140.5279388427734</v>
+        <v>140.5278778076172</v>
       </c>
       <c r="C140" t="n">
         <v>158.5099945068359</v>
@@ -4019,7 +4019,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>139.4029846191406</v>
+        <v>139.4030303955078</v>
       </c>
       <c r="C141" t="n">
         <v>156.7400054931641</v>
@@ -4048,7 +4048,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>146.1179046630859</v>
+        <v>146.1178894042969</v>
       </c>
       <c r="C142" t="n">
         <v>164.2899932861328</v>
@@ -4077,7 +4077,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>143.2629699707031</v>
+        <v>143.2629089355469</v>
       </c>
       <c r="C143" t="n">
         <v>161.0800018310547</v>
@@ -4106,7 +4106,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>164.5169372558594</v>
+        <v>164.5169219970703</v>
       </c>
       <c r="C144" t="n">
         <v>184.4299926757812</v>
@@ -4164,7 +4164,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>173.8296966552734</v>
+        <v>173.8297271728516</v>
       </c>
       <c r="C146" t="n">
         <v>194.8699951171875</v>
@@ -4193,7 +4193,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>170.7440338134766</v>
+        <v>170.7440185546875</v>
       </c>
       <c r="C147" t="n">
         <v>190.8999938964844</v>
@@ -4222,7 +4222,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>168.5348510742188</v>
+        <v>168.5348358154297</v>
       </c>
       <c r="C148" t="n">
         <v>188.4299926757812</v>
@@ -4280,7 +4280,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>177.8260803222656</v>
+        <v>177.8261108398438</v>
       </c>
       <c r="C150" t="n">
         <v>198.2400054931641</v>
@@ -4309,7 +4309,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>187.4601287841797</v>
+        <v>187.4601898193359</v>
       </c>
       <c r="C151" t="n">
         <v>208.9799957275391</v>
@@ -4338,7 +4338,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>196.1881713867188</v>
+        <v>196.1882171630859</v>
       </c>
       <c r="C152" t="n">
         <v>218.7100067138672</v>
@@ -4367,7 +4367,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>209.6424102783203</v>
+        <v>209.6424713134766</v>
       </c>
       <c r="C153" t="n">
         <v>233.1300048828125</v>
@@ -4396,7 +4396,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>211.2161560058594</v>
+        <v>211.2160949707031</v>
       </c>
       <c r="C154" t="n">
         <v>234.8800048828125</v>
@@ -4425,7 +4425,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>205.5957946777344</v>
+        <v>205.5958099365234</v>
       </c>
       <c r="C155" t="n">
         <v>228.6300048828125</v>
@@ -4454,7 +4454,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>208.4731750488281</v>
+        <v>208.4732055664062</v>
       </c>
       <c r="C156" t="n">
         <v>231.2799987792969</v>
@@ -4483,7 +4483,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>183.6219024658203</v>
+        <v>183.6218872070312</v>
       </c>
       <c r="C157" t="n">
         <v>203.7100067138672</v>
@@ -4512,7 +4512,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>193.4650726318359</v>
+        <v>193.4650573730469</v>
       </c>
       <c r="C158" t="n">
         <v>214.6300048828125</v>
@@ -4541,7 +4541,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>197.7023468017578</v>
+        <v>197.7023162841797</v>
       </c>
       <c r="C159" t="n">
         <v>218.7400054931641</v>
@@ -4599,7 +4599,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>221.9157562255859</v>
+        <v>221.9157257080078</v>
       </c>
       <c r="C161" t="n">
         <v>245.5299987792969</v>
@@ -4628,7 +4628,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>217.1228179931641</v>
+        <v>217.1227722167969</v>
       </c>
       <c r="C162" t="n">
         <v>239.5800018310547</v>
@@ -4657,7 +4657,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>239.4894104003906</v>
+        <v>239.4893951416016</v>
       </c>
       <c r="C163" t="n">
         <v>264.260009765625</v>
@@ -4686,7 +4686,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>249.7935943603516</v>
+        <v>249.7936859130859</v>
       </c>
       <c r="C164" t="n">
         <v>275.6300048828125</v>
@@ -4715,7 +4715,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>267.7213134765625</v>
+        <v>267.7213439941406</v>
       </c>
       <c r="C165" t="n">
         <v>294.760009765625</v>
@@ -4744,7 +4744,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>261.681396484375</v>
+        <v>261.6814270019531</v>
       </c>
       <c r="C166" t="n">
         <v>288.1099853515625</v>
@@ -4773,7 +4773,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>270.4420776367188</v>
+        <v>270.4420471191406</v>
       </c>
       <c r="C167" t="n">
         <v>297.1099853515625</v>
@@ -4802,7 +4802,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>272.899658203125</v>
+        <v>272.8996887207031</v>
       </c>
       <c r="C168" t="n">
         <v>299.8099975585938</v>
@@ -4831,7 +4831,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>267.5383911132812</v>
+        <v>267.5384216308594</v>
       </c>
       <c r="C169" t="n">
         <v>293.9200134277344</v>
@@ -4889,7 +4889,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>256.4450073242188</v>
+        <v>256.4450988769531</v>
       </c>
       <c r="C171" t="n">
         <v>281.1400146484375</v>
@@ -4918,7 +4918,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>260.0845031738281</v>
+        <v>260.0845947265625</v>
       </c>
       <c r="C172" t="n">
         <v>285.1300048828125</v>
@@ -4947,7 +4947,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>277.0163879394531</v>
+        <v>277.0163269042969</v>
       </c>
       <c r="C173" t="n">
         <v>303</v>
@@ -4976,7 +4976,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>282.0171813964844</v>
+        <v>282.0172424316406</v>
       </c>
       <c r="C174" t="n">
         <v>308.4700012207031</v>
@@ -5005,7 +5005,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>277.2082824707031</v>
+        <v>277.208251953125</v>
       </c>
       <c r="C175" t="n">
         <v>303.2099914550781</v>
@@ -5121,7 +5121,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>328.2852172851562</v>
+        <v>328.2853393554688</v>
       </c>
       <c r="C179" t="n">
         <v>357.6199951171875</v>
@@ -5150,7 +5150,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>359.6340637207031</v>
+        <v>359.6341247558594</v>
       </c>
       <c r="C180" t="n">
         <v>391.7699890136719</v>
@@ -5179,7 +5179,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>354.9334106445312</v>
+        <v>354.933349609375</v>
       </c>
       <c r="C181" t="n">
         <v>376.7799987792969</v>
@@ -5208,7 +5208,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>331.9953002929688</v>
+        <v>331.9952087402344</v>
       </c>
       <c r="C182" t="n">
         <v>352.4299926757812</v>
@@ -5237,7 +5237,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>312.4234924316406</v>
+        <v>312.4234619140625</v>
       </c>
       <c r="C183" t="n">
         <v>331</v>
@@ -5295,7 +5295,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>351.959716796875</v>
+        <v>351.9597473144531</v>
       </c>
       <c r="C185" t="n">
         <v>372.0899963378906</v>
@@ -5324,7 +5324,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>357.8053283691406</v>
+        <v>357.805419921875</v>
       </c>
       <c r="C186" t="n">
         <v>378.2699890136719</v>
@@ -5353,7 +5353,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>374.2640380859375</v>
+        <v>374.2640686035156</v>
       </c>
       <c r="C187" t="n">
         <v>395.6700134277344</v>
@@ -5382,7 +5382,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>407.2339172363281</v>
+        <v>407.23388671875</v>
       </c>
       <c r="C188" t="n">
         <v>429.7200012207031</v>
@@ -5411,7 +5411,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>431.6553344726562</v>
+        <v>431.6553649902344</v>
       </c>
       <c r="C189" t="n">
         <v>455.489990234375</v>
@@ -5440,7 +5440,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>425.8367309570312</v>
+        <v>425.8367004394531</v>
       </c>
       <c r="C190" t="n">
         <v>449.3500061035156</v>
@@ -5469,7 +5469,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>466.5725402832031</v>
+        <v>466.5726013183594</v>
       </c>
       <c r="C191" t="n">
         <v>491.5400085449219</v>
@@ -5498,7 +5498,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>511.9825134277344</v>
+        <v>511.9825439453125</v>
       </c>
       <c r="C192" t="n">
         <v>539.3800048828125</v>
@@ -5527,7 +5527,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>538.8640747070312</v>
+        <v>538.8641967773438</v>
       </c>
       <c r="C193" t="n">
         <v>567.7000122070312</v>
@@ -5556,7 +5556,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>479.4723815917969</v>
+        <v>479.4722290039062</v>
       </c>
       <c r="C194" t="n">
         <v>505.1300048828125</v>
@@ -5643,7 +5643,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>506.2990112304688</v>
+        <v>506.2989501953125</v>
       </c>
       <c r="C197" t="n">
         <v>531.719970703125</v>
@@ -5701,7 +5701,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>456.3661499023438</v>
+        <v>456.3660583496094</v>
       </c>
       <c r="C199" t="n">
         <v>479.2799987792969</v>
@@ -5730,7 +5730,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>516.3106079101562</v>
+        <v>516.3107299804688</v>
       </c>
       <c r="C200" t="n">
         <v>541.2999877929688</v>
@@ -5759,7 +5759,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>497.9969787597656</v>
+        <v>497.9969482421875</v>
       </c>
       <c r="C201" t="n">
         <v>522.0999755859375</v>
@@ -5788,7 +5788,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>450.4674987792969</v>
+        <v>450.4674682617188</v>
       </c>
       <c r="C202" t="n">
         <v>472.2699890136719</v>
@@ -5846,7 +5846,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>515.283935546875</v>
+        <v>515.2838745117188</v>
       </c>
       <c r="C204" t="n">
         <v>539.25</v>
@@ -5875,7 +5875,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>436.2114868164062</v>
+        <v>436.2115478515625</v>
       </c>
       <c r="C205" t="n">
         <v>456.5</v>
@@ -5904,7 +5904,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>488.4231872558594</v>
+        <v>488.4231567382812</v>
       </c>
       <c r="C206" t="n">
         <v>511.1400146484375</v>
@@ -5933,7 +5933,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>463.4667053222656</v>
+        <v>463.4667358398438</v>
       </c>
       <c r="C207" t="n">
         <v>484.1799926757812</v>
@@ -5962,7 +5962,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>475.6138000488281</v>
+        <v>475.6138305664062</v>
       </c>
       <c r="C208" t="n">
         <v>496.8699951171875</v>
@@ -5991,7 +5991,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>481.6921997070312</v>
+        <v>481.6922607421875</v>
       </c>
       <c r="C209" t="n">
         <v>503.2200012207031</v>
@@ -6020,7 +6020,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>490.6967163085938</v>
+        <v>490.6967468261719</v>
       </c>
       <c r="C210" t="n">
         <v>511.5599975585938</v>
@@ -6049,7 +6049,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>516.4229125976562</v>
+        <v>516.4229736328125</v>
       </c>
       <c r="C211" t="n">
         <v>538.3800048828125</v>
@@ -6078,7 +6078,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>537.8038330078125</v>
+        <v>537.803955078125</v>
       </c>
       <c r="C212" t="n">
         <v>560.6699829101562</v>
@@ -6107,7 +6107,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>527.8739013671875</v>
+        <v>527.8738403320312</v>
       </c>
       <c r="C213" t="n">
         <v>549.280029296875</v>
@@ -6136,7 +6136,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>542.9429321289062</v>
+        <v>542.9427490234375</v>
       </c>
       <c r="C214" t="n">
         <v>564.9600219726562</v>
@@ -6165,7 +6165,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>530.910888671875</v>
+        <v>530.9107666015625</v>
       </c>
       <c r="C215" t="n">
         <v>552.4400024414062</v>
@@ -6194,7 +6194,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>570.685546875</v>
+        <v>570.6856079101562</v>
       </c>
       <c r="C216" t="n">
         <v>592.739990234375</v>
@@ -6281,7 +6281,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>733.5753784179688</v>
+        <v>733.5755004882812</v>
       </c>
       <c r="C219" t="n">
         <v>743.8900146484375</v>
@@ -6368,7 +6368,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>799.9422607421875</v>
+        <v>799.9421997070312</v>
       </c>
       <c r="C222" t="n">
         <v>809.8900146484375</v>
@@ -6397,7 +6397,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>839.5497436523438</v>
+        <v>839.5496826171875</v>
       </c>
       <c r="C223" t="n">
         <v>849.989990234375</v>
@@ -6455,7 +6455,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>882.673828125</v>
+        <v>882.6739501953125</v>
       </c>
       <c r="C225" t="n">
         <v>892.3800048828125</v>
@@ -6484,7 +6484,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>876.8776245117188</v>
+        <v>876.8775634765625</v>
       </c>
       <c r="C226" t="n">
         <v>886.52001953125</v>
@@ -6513,7 +6513,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>864.671875</v>
+        <v>864.6717529296875</v>
       </c>
       <c r="C227" t="n">
         <v>874.1799926757812</v>
@@ -6542,7 +6542,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>962.5864868164062</v>
+        <v>962.5863647460938</v>
       </c>
       <c r="C228" t="n">
         <v>971.8800048828125</v>
@@ -6571,7 +6571,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>907.5081787109375</v>
+        <v>907.50830078125</v>
       </c>
       <c r="C229" t="n">
         <v>916.27001953125</v>
@@ -6600,7 +6600,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>970.5100708007812</v>
+        <v>970.5099487304688</v>
       </c>
       <c r="C230" t="n">
         <v>979.8800048828125</v>
@@ -6658,7 +6658,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>937.7711181640625</v>
+        <v>937.7710571289062</v>
       </c>
       <c r="C232" t="n">
         <v>945.780029296875</v>
@@ -6687,7 +6687,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>986.0784301757812</v>
+        <v>986.07861328125</v>
       </c>
       <c r="C233" t="n">
         <v>994.5</v>
@@ -6716,7 +6716,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>1032.715454101562</v>
+        <v>1032.715698242188</v>
       </c>
       <c r="C234" t="n">
         <v>1040.180053710938</v>
@@ -6745,7 +6745,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>982.8360595703125</v>
+        <v>982.8359985351562</v>
       </c>
       <c r="C235" t="n">
         <v>989.9400024414062</v>
@@ -6803,7 +6803,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>937.8480834960938</v>
+        <v>937.8480224609375</v>
       </c>
       <c r="C237" t="n">
         <v>943.3200073242188</v>
@@ -6861,7 +6861,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>907.4450073242188</v>
+        <v>907.4449462890625</v>
       </c>
       <c r="C239" t="n">
         <v>911.4500122070312</v>
@@ -6919,7 +6919,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>858.55078125</v>
+        <v>858.5507202148438</v>
       </c>
       <c r="C241" t="n">
         <v>862.3400268554688</v>
